--- a/excelCfg/buff.xlsx
+++ b/excelCfg/buff.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="buff" sheetId="1" r:id="R7571144ba1b34d5d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="buff" sheetId="1" r:id="R44da494d95604759"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1601,6 +1601,29 @@
         <x:v>ReplaceableTextures\CommandButtons\BTNManaBurn.blp</x:v>
       </x:c>
     </x:row>
+    <x:row r="27">
+      <x:c r="A27" t="str">
+        <x:v>B0E3</x:v>
+      </x:c>
+      <x:c r="B27" t="str">
+        <x:v>Broa</x:v>
+      </x:c>
+      <x:c r="C27" t="str">
+        <x:v>霜之哀伤·饥渴</x:v>
+      </x:c>
+      <x:c r="D27" t="str">
+        <x:v>普通攻击积攒的魂魄状态。最多 5 层；满层后的下一次攻击会触发强化斩击。具体层数见技能图标旁计数。</x:v>
+      </x:c>
+      <x:c r="E27" t="str">
+        <x:v>other</x:v>
+      </x:c>
+      <x:c r="F27" t="str">
+        <x:v>""</x:v>
+      </x:c>
+      <x:c r="G27" t="str">
+        <x:v>ui\selectHero\skills\a0e3.blp</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/excelCfg/buff.xlsx
+++ b/excelCfg/buff.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="buff" sheetId="1" r:id="R44da494d95604759"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="buff" sheetId="1" r:id="Rf5e58cbc0c5945ac"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1147,19 +1147,19 @@
         <x:v>B0N1</x:v>
       </x:c>
       <x:c r="B6" s="5" t="str">
-        <x:v>Bpoi</x:v>
+        <x:v>Bcri</x:v>
       </x:c>
       <x:c r="C6" s="5" t="str">
-        <x:v>风火灼烧</x:v>
+        <x:v>日灼迟滞</x:v>
       </x:c>
       <x:c r="D6" s="5" t="str">
-        <x:v>哪吒技能附带的减速与灼烧状态。</x:v>
+        <x:v>受到金乌灼痕爆发影响，移动速度降低 20%，持续 1 秒。</x:v>
       </x:c>
       <x:c r="E6" s="5" t="str">
         <x:v>other</x:v>
       </x:c>
       <x:c r="F6" s="5" t="str">
-        <x:v>""</x:v>
+        <x:v>Abilities\Spells\Human\FlameStrike\FlameStrikeTarget.mdl</x:v>
       </x:c>
       <x:c r="G6" s="5"/>
     </x:row>
@@ -1171,10 +1171,10 @@
         <x:v>Broa</x:v>
       </x:c>
       <x:c r="C7" s="5" t="str">
-        <x:v>三头六臂</x:v>
+        <x:v>日痕</x:v>
       </x:c>
       <x:c r="D7" s="5" t="str">
-        <x:v>哪吒施法后的普攻强化层。</x:v>
+        <x:v>后羿的普通攻击和技能命中会叠加日痕；叠满后发生爆发并清除。</x:v>
       </x:c>
       <x:c r="E7" s="5" t="str">
         <x:v>other</x:v>
